--- a/framework/data/excel/locators.xlsx
+++ b/framework/data/excel/locators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF099292-376C-4695-A9C1-EE9A8EB14074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560C8A77-FF36-4C60-AA0F-7173D6D3CB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="930" yWindow="2520" windowWidth="12450" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>Page</t>
   </si>
@@ -73,6 +73,36 @@
   </si>
   <si>
     <t>errorMessage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search </t>
+  </si>
+  <si>
+    <t>searchBox</t>
+  </si>
+  <si>
+    <t>searchButton</t>
+  </si>
+  <si>
+    <t>noRowsMessage</t>
+  </si>
+  <si>
+    <t>//div[@id='searchBox-wrapper']/div/div/button</t>
+  </si>
+  <si>
+    <t>//div[@id='root']/div/div/div/div[2]/div/div[2]/div/div/span</t>
+  </si>
+  <si>
+    <t>//*[@id="root"]/div/div/div/div[2]/div[1]/div[2]/table/tbody/tr[1]</t>
+  </si>
+  <si>
+    <t>resultTable</t>
+  </si>
+  <si>
+    <t>//*[@id="root"]/div/div/div/div[2]/div[1]/div[2]/table/tbody/tr[1]/td[2]/div/span</t>
+  </si>
+  <si>
+    <t>firstResultTitle</t>
   </si>
 </sst>
 </file>
@@ -431,13 +461,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="63.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -525,6 +555,76 @@
         <v>12</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/framework/data/excel/locators.xlsx
+++ b/framework/data/excel/locators.xlsx
@@ -1,148 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560C8A77-FF36-4C60-AA0F-7173D6D3CB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="2520" windowWidth="12450" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="930" yWindow="2520" windowWidth="12450" windowHeight="13185" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="demoQA" sheetId="1" r:id="rId1"/>
+    <sheet name="demoQA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
-  <si>
-    <t>Page</t>
-  </si>
-  <si>
-    <t>Element</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>login</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>userName</t>
-  </si>
-  <si>
-    <t>CSS_SELECTOR</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>button[type='submit']</t>
-  </si>
-  <si>
-    <t>userName-value</t>
-  </si>
-  <si>
-    <t>#flash.error</t>
-  </si>
-  <si>
-    <t>loginButton</t>
-  </si>
-  <si>
-    <t>userNameLabel</t>
-  </si>
-  <si>
-    <t>errorMessage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">search </t>
-  </si>
-  <si>
-    <t>searchBox</t>
-  </si>
-  <si>
-    <t>searchButton</t>
-  </si>
-  <si>
-    <t>noRowsMessage</t>
-  </si>
-  <si>
-    <t>//div[@id='searchBox-wrapper']/div/div/button</t>
-  </si>
-  <si>
-    <t>//div[@id='root']/div/div/div/div[2]/div/div[2]/div/div/span</t>
-  </si>
-  <si>
-    <t>//*[@id="root"]/div/div/div/div[2]/div[1]/div[2]/table/tbody/tr[1]</t>
-  </si>
-  <si>
-    <t>resultTable</t>
-  </si>
-  <si>
-    <t>//*[@id="root"]/div/div/div/div[2]/div[1]/div[2]/table/tbody/tr[1]/td[2]/div/span</t>
-  </si>
-  <si>
-    <t>firstResultTitle</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="13"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -175,26 +82,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -460,173 +426,265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="63.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col width="21.28515625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="21.7109375" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20.28515625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="63.28515625" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9.140625" customWidth="1" style="1" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>userName</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>loginButton</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>userNameLabel</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>userName-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>errorMessage</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search </t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>searchBox</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>searchBox</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search </t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>searchButton</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>CSS_SELECTOR</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>//div[@id='searchBox-wrapper']/div/div/button</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search </t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>noRowsMessage</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>CSS_SELECTOR</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>//div[@id='root']/div/div/div/div[2]/div/div[2]/div/div/span</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search </t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>resultTable</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>CSS_SELECTOR</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>//*[@id="root"]/div/div/div/div[2]/div[1]/div[2]/table/tbody/tr[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search </t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>firstResultTitle</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>CSS_SELECTOR</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>//*[@id="root"]/div/div/div/div[2]/div[1]/div[2]/table/tbody/tr[1]/td[2]/div/span</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>